--- a/docs/economics.xlsx
+++ b/docs/economics.xlsx
@@ -343,7 +343,7 @@
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>FX·King</author>
+    <author>Rebound</author>
   </authors>
   <commentList>
     <comment ref="B5" authorId="0" shapeId="0">
@@ -726,7 +726,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>FX·KING — GAZDASÁGI MODELL</t>
+          <t>REBOUND — GAZDASÁGI MODELL</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
